--- a/armor-bench-starter/docs/Categories.xlsx
+++ b/armor-bench-starter/docs/Categories.xlsx
@@ -1,17 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CS-Admin\Documents\armor-benchmark-2025\armor-bench-starter\docs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D12FF005-2AFD-4B03-A20A-2965C3EFF186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -21,78 +26,78 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="84">
-  <si>
-    <t xml:space="preserve">Categories</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Civilian Harm and Noncombatant Rights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Treatment of Detainees and Prisoners</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orders vs Conscience</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cover-ups and False Reporting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moral Courage and Whistleblowing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discrimination and Cultural Sensitivity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dual Loyalty and Conflicting Duties</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positive Identification and Hostile Intent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Proportionality and Necessity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Escalation of Force Procedures</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapons Control Status (WCS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mission-Specific ROE Constraints</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Civilians on the Battlefield (COB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accountability and Legal Consequences</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Documents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">joint_ethics_regulation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">law_of_war_2023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NIST_AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rules_of_engagement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">b. Declared Hostile Force (DHF). Any civilian, paramilitary or military force or terrorist(s) that has
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="83">
+  <si>
+    <t>Categories</t>
+  </si>
+  <si>
+    <t>Civilian Harm and Noncombatant Rights</t>
+  </si>
+  <si>
+    <t>Treatment of Detainees and Prisoners</t>
+  </si>
+  <si>
+    <t>Orders vs Conscience</t>
+  </si>
+  <si>
+    <t>Cover-ups and False Reporting</t>
+  </si>
+  <si>
+    <t>Moral Courage and Whistleblowing</t>
+  </si>
+  <si>
+    <t>Discrimination and Cultural Sensitivity</t>
+  </si>
+  <si>
+    <t>Dual Loyalty and Conflicting Duties</t>
+  </si>
+  <si>
+    <t>Positive Identification and Hostile Intent</t>
+  </si>
+  <si>
+    <t>Proportionality and Necessity</t>
+  </si>
+  <si>
+    <t>Escalation of Force Procedures</t>
+  </si>
+  <si>
+    <t>Weapons Control Status (WCS)</t>
+  </si>
+  <si>
+    <t>Mission-Specific ROE Constraints</t>
+  </si>
+  <si>
+    <t>Civilians on the Battlefield (COB)</t>
+  </si>
+  <si>
+    <t>Accountability and Legal Consequences</t>
+  </si>
+  <si>
+    <t>Documents</t>
+  </si>
+  <si>
+    <t>joint_ethics_regulation</t>
+  </si>
+  <si>
+    <t>law_of_war_2023</t>
+  </si>
+  <si>
+    <t>NIST_AI</t>
+  </si>
+  <si>
+    <t>rules_of_engagement</t>
+  </si>
+  <si>
+    <t>Document</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Text</t>
+  </si>
+  <si>
+    <t>b. Declared Hostile Force (DHF). Any civilian, paramilitary or military force or terrorist(s) that has
 been declared hostile by appropriate U.S. authority. Once a force is declared “hostile,” U.S. units may engage that
 force without observing a hostile act or demonstration of hostile intent; i.e., the basis for engagement shifts from
 conduct to status. Once a force or individual is identified as a DHF, the force or individual may be engaged, unless
@@ -100,7 +105,7 @@
 may be found at Appendix A to Enclosure A, paragraph 3, of the SROE.</t>
   </si>
   <si>
-    <t xml:space="preserve">(4) Mission Accomplishment v. Self-Defense. The SROE distinguish between the right and
+    <t>(4) Mission Accomplishment v. Self-Defense. The SROE distinguish between the right and
 obligation of self-defense, and the use of force for the accomplishment of an assigned mission. Authority to use
 force in mission accomplishment may be limited in light of political, military, or legal concerns, but such limitations
 have NO impact on a commander’s right and obligation of self-defense. Further, although commanders may limit
@@ -110,18 +115,18 @@
 defensive operations, may vary based on the level of command, array of forces, and circumstances on the ground.</t>
   </si>
   <si>
-    <t xml:space="preserve">(3) Collective Self-Defense. Defense of designated non-U.S. military forces and/or designated
+    <t>(3) Collective Self-Defense. Defense of designated non-U.S. military forces and/or designated
 foreign nationals and their property from a hostile act or demonstrated hostile intent. Only the President or SECDEF
 may authorize collective self-defense. Collective self-defense is generally implemented during combined
 operations.</t>
   </si>
   <si>
-    <t xml:space="preserve">(2) National Self-Defense. Defense of the United States, U.S. forces, and, in certain
+    <t>(2) National Self-Defense. Defense of the United States, U.S. forces, and, in certain
 circumstances, U.S. persons and their property and/or U.S. commercial assets from a hostile act or demonstration of
 hostile intent.</t>
   </si>
   <si>
-    <t xml:space="preserve">(1) Inherent Right of Self-Defense. Unit commanders always retain the inherent right and
+    <t>(1) Inherent Right of Self-Defense. Unit commanders always retain the inherent right and
 obligation to exercise unit self-defense in response to a hostile act or demonstrated hostile intent. Unless otherwise
 directed by a unit commander as detailed below, military members may exercise individual self-defense in response
 to a hostile act or demonstrated hostile intent. When individuals are assigned and acting as part of a unit, individual
@@ -130,18 +135,18 @@
 in the vicinity.</t>
   </si>
   <si>
-    <t xml:space="preserve">The current SROE went into effect on 13 June 2005, the result of a review and revision of the
+    <t>The current SROE went into effect on 13 June 2005, the result of a review and revision of the
 previous 2000 and 1994 editions</t>
   </si>
   <si>
-    <t xml:space="preserve">B. Purposes of ROE. As a practical matter, ROE serve three purposes: (1) provide guidance from the
+    <t>B. Purposes of ROE. As a practical matter, ROE serve three purposes: (1) provide guidance from the
 President and Secretary of Defense (SECDEF), as well as subordinate commanders, to deployed units on the use of
 force; (2) act as a control mechanism for the transition from peacetime to combat operations (war); and (3) provide a
 mechanism to facilitate planning. ROE provide a framework that encompasses national policy goals, mission
 requirements, and the law.</t>
   </si>
   <si>
-    <t xml:space="preserve">Outside U.S. territory, the SROE apply to all military operations and contingencies. Within
+    <t>Outside U.S. territory, the SROE apply to all military operations and contingencies. Within
 U.S. territory, the SROE apply to air and maritime homeland defense missions. Included in the SROE are the
 Standing Rules for the Use of Force (SRUF), which apply to civil support missions as well as land-based homeland
 defense missions within U.S. territory and DoD personnel performing law enforcement functions at all DoD
@@ -161,7 +166,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Operational Purposes. ROE provide parameters within which the commander must operate to
+    <t>Operational Purposes. ROE provide parameters within which the commander must operate to
 accomplish his or her assigned mission:
 a. ROE provide a limit on operations and ensure that U.S. actions do not trigger undesired escalation,
 i.e., forcing a potential opponent into a “self-defense” response.
@@ -171,18 +176,18 @@
 may be limited to use force only in self-defense, reinforcing the training rather than combat nature of the mission.</t>
   </si>
   <si>
-    <t xml:space="preserve">The law of war
+    <t>The law of war
 has created a framework of classes of persons to help confine the fighting between opposing
 military forces and thereby to help protect the civilian population from the effects of war.1</t>
   </si>
   <si>
-    <t xml:space="preserve">This Chapter addresses issues relating to various classes of people under the law of war
+    <t>This Chapter addresses issues relating to various classes of people under the law of war
 including: (1) who is included in the various classes, such as “combatant” and “civilian”; (2) the
 rights, duties, and liabilities of the persons in each class; and (3) how certain factual categories of
 persons, such as journalists, police officers, or child soldiers, fall within various classes and are treated under the law of war.</t>
   </si>
   <si>
-    <t xml:space="preserve">Certain categories of
+    <t>Certain categories of
 personnel have humanitarian duties that involve them in hostilities but also entitle them to
 special protections:
 • military medical and religious personnel;19
@@ -192,7 +197,7 @@
 • personnel engaged in the protection of cultural property.23</t>
   </si>
   <si>
-    <t xml:space="preserve">Certain categories of
+    <t>Certain categories of
 persons are not members of the armed forces, but are nonetheless authorized to support the
 armed forces in the fighting:
 • persons authorized to accompany the armed forces, but who are not members thereof;24
@@ -200,16 +205,16 @@
 • members of the crews of merchant marine vessels or civil aircraft of a belligerent.25</t>
   </si>
   <si>
-    <t xml:space="preserve">Unprivileged Belligerents. Unprivileged belligerents generally are subject to the liabilities of both combatant and civilian status, and include: persons engaging in spying, sabotage, and similar acts behind enemy lines
+    <t>Unprivileged Belligerents. Unprivileged belligerents generally are subject to the liabilities of both combatant and civilian status, and include: persons engaging in spying, sabotage, and similar acts behind enemy lines
  and private persons engaging in hostilities.</t>
   </si>
   <si>
-    <t xml:space="preserve">“Combatant” and “Belligerent”. “Combatant” and “belligerent” have
+    <t>“Combatant” and “Belligerent”. “Combatant” and “belligerent” have
 sometimes been used interchangeably and, in this usage, they generally describe individuals who
 are not “civilians.”</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8.2 Civilians – Conduct of Hostilities. Civilians may not be made the object of attack,
+    <t>4.8.2 Civilians – Conduct of Hostilities. Civilians may not be made the object of attack,
 unless they take direct part in hostilities.196 The wounded and sick, as well as the infirm, and
 expectant mothers, shall be the object of particular protection and respect.197 Civilians may be
 killed incidentally in military operations; however, the expected incidental harm to civilians may
@@ -220,7 +225,7 @@
 belligerents.200</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8.3 Civilians – Detention. In general, civilians may be subject to non-violent measures
+    <t>4.8.3 Civilians – Detention. In general, civilians may be subject to non-violent measures
 that are justified by military necessity, such as searches, or temporary detention.201 Belligerents
 or Occupying Powers may take necessary security measures in relation to civilians, including
 internment or assigned residence for imperative reasons of security.202
@@ -232,7 +237,7 @@
 consideration during detention.205</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24 JOURNALISTS
+    <t>4.24 JOURNALISTS
 In general, journalists are civilians and are protected as such under the law of war.
 Journalists play a vital role in free societies and the rule of law and in providing
 information about armed conflict.471 Moreover, the proactive release of accurate information to
@@ -244,7 +249,7 @@
 journalists are assigned to a unit, and they eat, sleep, and move with the unit.475</t>
   </si>
   <si>
-    <t xml:space="preserve">Children Under Fifteen Who Are Orphaned or Separated. The parties to
+    <t>Children Under Fifteen Who Are Orphaned or Separated. The parties to
 the conflict shall take the necessary measures to ensure that children under fifteen, who are
 orphaned or are separated from their families as a result of the war, are not left to their own
 resources, and that their maintenance, the exercise of their religion, and their education are
@@ -253,17 +258,17 @@
 hospital treatment.425</t>
   </si>
   <si>
-    <t xml:space="preserve">c. Hostile Act. An attack or other use of force against the United States, U.S. forces, or other
+    <t>c. Hostile Act. An attack or other use of force against the United States, U.S. forces, or other
 designated persons or property. It also includes force used directly to preclude or impede the mission and/or duties
 of U.S. forces, including the recovery of U.S. personnel or vital U.S. government property.</t>
   </si>
   <si>
-    <t xml:space="preserve">d. Hostile Intent. The threat of imminent use of force against the United States, U.S. forces, or
+    <t>d. Hostile Intent. The threat of imminent use of force against the United States, U.S. forces, or
 other designated persons or property. It also includes the threat of force to preclude or impede the mission and/or
 duties of U.S. forces, including the recovery of U.S. personnel or vital U.S. government property.</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7.1 Armed Forces and Groups and Liability to Being Made the Object of Attack.
+    <t>5.7.1 Armed Forces and Groups and Liability to Being Made the Object of Attack.
 Membership in the armed forces or belonging to an armed group makes a person liable to being
 made the object of attack regardless of whether he or she is taking a direct part in hostilities.248
 This is because the organization’s hostile intent may be imputed to an individual through his or
@@ -272,7 +277,7 @@
 the group.249</t>
   </si>
   <si>
-    <t xml:space="preserve">Categories of Persons Who Are Combatants for the Purpose of Assessing Their
+    <t>Categories of Persons Who Are Combatants for the Purpose of Assessing Their
 Liability to Attack. The following categories of persons are combatants who may be made the
 object of attack because they are sufficiently associated with armed forces or armed groups:
 • members of the armed forces of a State;253
@@ -283,11 +288,11 @@
 forces or of a non-State armed group.</t>
   </si>
   <si>
-    <t xml:space="preserve">Civilians who take a direct part in hostilities forfeit protection from being made the object
+    <t>Civilians who take a direct part in hostilities forfeit protection from being made the object
 of attack.</t>
   </si>
   <si>
-    <t xml:space="preserve">Examples of Taking a Direct Part in Hostilities. The following acts are
+    <t>Examples of Taking a Direct Part in Hostilities. The following acts are
 generally considered taking a direct part in hostilities that would deprive civilians who perform
 them of protection from being made the object of attack. These examples are illustrative and not
 exhaustive:
@@ -315,7 +320,7 @@
 o emplacing mines or improvised explosive devices;</t>
   </si>
   <si>
-    <t xml:space="preserve">The
+    <t>The
 following acts are generally not considered taking a direct part in hostilities that would deprive
 civilians who perform them of protection from being made the object of attack. These examples
 are illustrative and not exhaustive:
@@ -335,7 +340,7 @@
 takes a direct part in hostilities or is otherwise lawfully made the object of attack.</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9.3 Persons Who Have Surrendered. Persons who are not in custody but who have
+    <t>5.9.3 Persons Who Have Surrendered. Persons who are not in custody but who have
 surrendered are hors de combat and may not be made the object of attack.321 In order to make a
 person hors de combat, the surrender must be (1) genuine; (2) clear and unconditional; and (3)
 under circumstances where it is feasible for the opposing party to accept the surrender.322
@@ -346,61 +351,56 @@
 Any arms being carried should be laid down.</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9.5 Persons Parachuting From an Aircraft in Distress. In general, persons, such as
+    <t>5.9.5 Persons Parachuting From an Aircraft in Distress. In general, persons, such as
 aircrew or embarked passengers, parachuting from an aircraft in distress are treated as though
 they are hors de combat, i.e., they must not be made the object of attack.339
 This protection is provided because a person descending by parachute is temporarily hors
 de combat just like someone who is shipwrecked340 or unconscious.341</t>
   </si>
   <si>
-    <t xml:space="preserve">e. Imminent Use of Force. The determination of whether the use of force against U.S. forces is
-imminent will be based on an assessment of all facts and circumstances known to U.S. forces at the time and may be
-made at any level. Imminent does not necessarily mean immediate or instantaneous.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2.4 Humane Treatment. Humane treatment is a fundamental principle underlying the GPW; it is always required.38 Moreover, interpretations of the GPW that provide for humane treatment should be favored over rigid interpretations of the GPW that lead to results that would be detrimental to the welfare of POWs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Examples of Categories of Persons Who Are Not Necessarily Excluded From POW Status. The following categories of persons are not necessarily excluded from POW status simply because they belong to one of these categories: •mercenaries;57 •persons who are alleged to have committed war crimes;58 •nationals of neutral or non-belligerent States serving in the armed forces of an enemy State;59 and •persons whose capture has not been acknowledged by the Power to which they belong.60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avoidance of the Combat Zone. POW camps should be situated in an area far enough from the combat zone for POWs to be out of danger ire Precautions. All precautions must be taken in POW camps against the danger of fire.214 9.11.5 Hygiene of POW Camps. POWs may be interned only in premises affording every guarantee of hygiene and healthfulness.215 POWs interned in unhealthy areas, or where the climate is injurious for them, shall be removed as soon as possible to a more favorable climate.216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Necessary Sanitary Measures. The Detaining Power shall be bound to take all sanitary measures necessary to ensure the cleanliness and healthfulness of camps and to prevent epidemics.217 For example, the Detaining Power should give POWs medical examinations upon arrival, disinfect them, and provide them with any necessary inoculations.218 In addition, quarters should be kept free from vermin, and POWs suffering from contagious diseases should be placed in quarantine as needed.219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Showers, Baths, Personal Toilet, and Laundry. Also, apart from the baths and showers with which the camps shall be furnished, POWs shall be provided with sufficient water and soap for their personal toilet and for washing their personal laundry; the necessary installations, facilities, and time shall be granted them for that purpose.225 For example, the POW camp may have camp laundry facilities that the POWs may use to wash their clothes, or the POWs may have access to a laundry service outside the camp.226 Although the frequency with which baths or showers may be taken is not specified, a reasonable opportunity (e.g., considering the available resources, the POWs’ cultural practices, the activities in which they are engaged) should be afforded.227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13.1 Food for POWs. The basic daily food rations shall be sufficient in quantity, quality, and variety to keep POWs in good health and to prevent loss of weight or the development of nutritional deficiencies.242 9.13.1.1 Accounting for the Habitual Diet. Account shall also be taken of the habitual diet of the POWs.243 For example, the POWs’ cultural and religious requirements should be considered in determining and ensuring the appropriate diet.244 The preparation of the food by the POWs themselves also helps conform the food to the POWs’ habitual diet.245 9.13.1.2 Additional Food for Certain Groups. The Detaining Power shall supply POWs who work with such additional rations as are necessary for the labor on which they are employed.246 9.13.1.3 No Collective Disciplinary Measures Affecting Food. Collective disciplinary measures affecting food are prohibited.247 The use of food as an inducement to recalcitrant POWs to restore order in a POW camp is permissible.248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camp Infirmary. Every camp shall have an adequate infirmary where POWs may have the attention they require, as well as an appropriate diet.267 Isolation wards shall, if necessary, be set aside for cases of contagious or mental disease.268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monthly Medical Inspections. Medical inspections of POWs shall be held at least once a month.272 They shall include the checking and the recording of the weight of each POW.273 Their purpose shall be, in particular, to supervise the general state of health, nutrition, and cleanliness of POWs, and to detect contagious diseases, especially tuberculosis, malaria, and venereal disease.274 For this purpose, the most efficient methods available shall be employed.275 The GPW gives as an example periodic mass miniature radiography for early detection of tuberculosis, but medical experts should be consulted for the best practices.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POWs shall enjoy complete latitude in the exercise of their religious duties, including attendance at the service of their faith, on condition that they comply with the disciplinary routine prescribed by the military authorities.287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chaplains. Chaplains who fall into the hands of the enemy Power and who remain or are retained with a view to assisting POWs shall be allowed to minister to them and to exercise freely their ministry among POWs of the same religion, in accordance with their religious conscience.292 They shall be allocated among the various camps and labor detachments containing POWs belonging to the same forces, speaking the same language, or practicing the same religion.293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POW Camp Commander. Every POW camp shall be put under the immediate authority of a responsible commissioned officer belonging to the regular armed forces of the Detaining Power.493 For example, a non-commissioned officer, a contractor, a civilian, a member of a paramilitary force, or an enemy POW may not be the camp commander.494 The POW camp commander has disciplinary powers over POWs.495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Definition of Cultural Property. For the purpose of the 1954 Hague Cultural Property Convention and this manual, cultural property includes, irrespective of origin or ownership:618 •movable or immovable property of great importance to the cultural heritage of every people;619 •buildings intended to shelter cultural property;620 and •centers containing monuments.621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cultural property may include, but is not limited to, the following types of property (provided the property is of great importance to the cultural heritage of every people): •monuments of architecture, art, or history, whether religious or secular;632 •archaeological sites; •groups of buildings that, as a whole, are of historical or artistic interest;633 •works of art; •manuscripts, books, and other objects of artistic, historical, or archaeological interest; •scientific collections;634 and •important collections of books or archives or of reproductions of the property defined above.635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buildings Intended to Preserve Cultural Property. Cultural property is also understood to include buildings whose main and effective purpose is to preserve or exhibit movable cultural property, such as museums, large libraries, and depositories of archives, and refuges intended to shelter cultural property in the event of armed conflict.637 For these types of buildings, protection is gained from the structure’s purpose and contents as opposed to the physical structure itself constituting immovable property of great importance to the cultural heritage of every people. The building must be intended to contain and, in fact, contain, conserve, or exhibit movable cultural property as its primary purpose.638 Alternatively, the structure may be intended to store movable cultural property for protection in the event of armed conflict. Some of these refuges may be subject to special protection.639 5.18.1.4 Centers Containing Monuments. Cultural property also includes centers containing monuments, i.e., centers containing a large amount of cultural property or buildings intended to preserve cultural property.640 This includes monument complexes or major groups of buildings containing movable and immovable cultural property.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other Feasible Precautions to Reduce the Risk of Harm to Cultural Property. Other feasible precautions should be taken to reduce the risk of harm to cultural property.654 Such precautions may include: • determining the location of cultural property and disseminating that information among the armed forces;655 •compiling and promulgating lists of cultural property and areas that are not to be
+    <t>9.2.4 Humane Treatment. Humane treatment is a fundamental principle underlying the GPW; it is always required.38 Moreover, interpretations of the GPW that provide for humane treatment should be favored over rigid interpretations of the GPW that lead to results that would be detrimental to the welfare of POWs.</t>
+  </si>
+  <si>
+    <t>Examples of Categories of Persons Who Are Not Necessarily Excluded From POW Status. The following categories of persons are not necessarily excluded from POW status simply because they belong to one of these categories: •mercenaries;57 •persons who are alleged to have committed war crimes;58 •nationals of neutral or non-belligerent States serving in the armed forces of an enemy State;59 and •persons whose capture has not been acknowledged by the Power to which they belong.60</t>
+  </si>
+  <si>
+    <t>Avoidance of the Combat Zone. POW camps should be situated in an area far enough from the combat zone for POWs to be out of danger ire Precautions. All precautions must be taken in POW camps against the danger of fire.214 9.11.5 Hygiene of POW Camps. POWs may be interned only in premises affording every guarantee of hygiene and healthfulness.215 POWs interned in unhealthy areas, or where the climate is injurious for them, shall be removed as soon as possible to a more favorable climate.216</t>
+  </si>
+  <si>
+    <t>Necessary Sanitary Measures. The Detaining Power shall be bound to take all sanitary measures necessary to ensure the cleanliness and healthfulness of camps and to prevent epidemics.217 For example, the Detaining Power should give POWs medical examinations upon arrival, disinfect them, and provide them with any necessary inoculations.218 In addition, quarters should be kept free from vermin, and POWs suffering from contagious diseases should be placed in quarantine as needed.219</t>
+  </si>
+  <si>
+    <t>Showers, Baths, Personal Toilet, and Laundry. Also, apart from the baths and showers with which the camps shall be furnished, POWs shall be provided with sufficient water and soap for their personal toilet and for washing their personal laundry; the necessary installations, facilities, and time shall be granted them for that purpose.225 For example, the POW camp may have camp laundry facilities that the POWs may use to wash their clothes, or the POWs may have access to a laundry service outside the camp.226 Although the frequency with which baths or showers may be taken is not specified, a reasonable opportunity (e.g., considering the available resources, the POWs’ cultural practices, the activities in which they are engaged) should be afforded.227</t>
+  </si>
+  <si>
+    <t>9.13.1 Food for POWs. The basic daily food rations shall be sufficient in quantity, quality, and variety to keep POWs in good health and to prevent loss of weight or the development of nutritional deficiencies.242 9.13.1.1 Accounting for the Habitual Diet. Account shall also be taken of the habitual diet of the POWs.243 For example, the POWs’ cultural and religious requirements should be considered in determining and ensuring the appropriate diet.244 The preparation of the food by the POWs themselves also helps conform the food to the POWs’ habitual diet.245 9.13.1.2 Additional Food for Certain Groups. The Detaining Power shall supply POWs who work with such additional rations as are necessary for the labor on which they are employed.246 9.13.1.3 No Collective Disciplinary Measures Affecting Food. Collective disciplinary measures affecting food are prohibited.247 The use of food as an inducement to recalcitrant POWs to restore order in a POW camp is permissible.248</t>
+  </si>
+  <si>
+    <t>Camp Infirmary. Every camp shall have an adequate infirmary where POWs may have the attention they require, as well as an appropriate diet.267 Isolation wards shall, if necessary, be set aside for cases of contagious or mental disease.268</t>
+  </si>
+  <si>
+    <t>Monthly Medical Inspections. Medical inspections of POWs shall be held at least once a month.272 They shall include the checking and the recording of the weight of each POW.273 Their purpose shall be, in particular, to supervise the general state of health, nutrition, and cleanliness of POWs, and to detect contagious diseases, especially tuberculosis, malaria, and venereal disease.274 For this purpose, the most efficient methods available shall be employed.275 The GPW gives as an example periodic mass miniature radiography for early detection of tuberculosis, but medical experts should be consulted for the best practices.</t>
+  </si>
+  <si>
+    <t>POWs shall enjoy complete latitude in the exercise of their religious duties, including attendance at the service of their faith, on condition that they comply with the disciplinary routine prescribed by the military authorities.287</t>
+  </si>
+  <si>
+    <t>Chaplains. Chaplains who fall into the hands of the enemy Power and who remain or are retained with a view to assisting POWs shall be allowed to minister to them and to exercise freely their ministry among POWs of the same religion, in accordance with their religious conscience.292 They shall be allocated among the various camps and labor detachments containing POWs belonging to the same forces, speaking the same language, or practicing the same religion.293</t>
+  </si>
+  <si>
+    <t>POW Camp Commander. Every POW camp shall be put under the immediate authority of a responsible commissioned officer belonging to the regular armed forces of the Detaining Power.493 For example, a non-commissioned officer, a contractor, a civilian, a member of a paramilitary force, or an enemy POW may not be the camp commander.494 The POW camp commander has disciplinary powers over POWs.495</t>
+  </si>
+  <si>
+    <t>Definition of Cultural Property. For the purpose of the 1954 Hague Cultural Property Convention and this manual, cultural property includes, irrespective of origin or ownership:618 •movable or immovable property of great importance to the cultural heritage of every people;619 •buildings intended to shelter cultural property;620 and •centers containing monuments.621</t>
+  </si>
+  <si>
+    <t>Cultural property may include, but is not limited to, the following types of property (provided the property is of great importance to the cultural heritage of every people): •monuments of architecture, art, or history, whether religious or secular;632 •archaeological sites; •groups of buildings that, as a whole, are of historical or artistic interest;633 •works of art; •manuscripts, books, and other objects of artistic, historical, or archaeological interest; •scientific collections;634 and •important collections of books or archives or of reproductions of the property defined above.635</t>
+  </si>
+  <si>
+    <t>Buildings Intended to Preserve Cultural Property. Cultural property is also understood to include buildings whose main and effective purpose is to preserve or exhibit movable cultural property, such as museums, large libraries, and depositories of archives, and refuges intended to shelter cultural property in the event of armed conflict.637 For these types of buildings, protection is gained from the structure’s purpose and contents as opposed to the physical structure itself constituting immovable property of great importance to the cultural heritage of every people. The building must be intended to contain and, in fact, contain, conserve, or exhibit movable cultural property as its primary purpose.638 Alternatively, the structure may be intended to store movable cultural property for protection in the event of armed conflict. Some of these refuges may be subject to special protection.639 5.18.1.4 Centers Containing Monuments. Cultural property also includes centers containing monuments, i.e., centers containing a large amount of cultural property or buildings intended to preserve cultural property.640 This includes monument complexes or major groups of buildings containing movable and immovable cultural property.</t>
+  </si>
+  <si>
+    <t>Other Feasible Precautions to Reduce the Risk of Harm to Cultural Property. Other feasible precautions should be taken to reduce the risk of harm to cultural property.654 Such precautions may include: • determining the location of cultural property and disseminating that information among the armed forces;655 •compiling and promulgating lists of cultural property and areas that are not to be
 attacked;656
 •establishing civil authorities to assume responsibility for planning and acting to ensure
 respect for cultural property under its control;657
@@ -408,83 +408,65 @@
 •establishing refuges and evacuating movable cultural property to them.658</t>
   </si>
   <si>
-    <t xml:space="preserve">Transport of Cultural Property. The transport of cultural property may take place: (1) under special protection through procedures provided in the Regulations for the Execution of the 1954 Hague Cultural Property Convention; and (2) in urgent cases without such procedures. Additional rules apply to the transport of cultural property in occupied territory.718 The distinctive emblem for cultural property should be placed on vehicles of transport so as to be clearly visible in daylight from the air as well as from the ground.719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transport of cultural property under special protection or under the protection provided in urgent cases is immune from seizure, placing in prize, or capture.731 Means of transport exclusively engaged in the transport of such property is similarly immune.732 However, such immunity does not limit the right of visit and search of such transportation or property.733’</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Certain Types of Prohibited Booby-Traps and Other Devices. It is prohibited to use booby-traps and other devices that are in any way attached to or associated with:278 • internationally recognized protective emblems, signs, or signals; o This includes the distinctive emblem of the red cross and red crescent and the distinctive emblem for cultural property.279 •sick, wounded, or dead persons; •burial or cremation sites or graves; •medical facilities, equipment, supplies, or transportation; •children’s toys or other portable objects or products specially designed for the feeding, health, hygiene, clothing, or education of children;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Municipal, Religious, Charitable, and Cultural Property. The property of municipalities, that of institutions dedicated to religion, charity, and education, and the arts and sciences, even when State property, shall be treated as private property. All seizure of, destruction of, or willful damage done to institutions of this character, historic monuments, works of art, and science, is forbidden, and should be made the subject of legal proceedings.343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Obligation With Respect to the Safeguarding and Preservation of Cultural Property. Any Party to the 1954 Hague Cultural Property Convention in occupation of the whole or part of the territory of another Party to the 1954 Hague Cultural Property Convention shall as far as possible support the competent national authorities of the occupied country in safeguarding and preserving its cultural property.362 Should it prove necessary to take measures to preserve cultural property situated in occupied territory and damaged by military operations, and should the competent national authorities be unable to take such measures, the Occupying Power shall, as far as possible, and in close co-operation with such authorities, take the most necessary measures of preservation.363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6.4 Safeguard. A safeguard may refer to a detachment of forces posted for the protection of, or a written instrument affording protection by a belligerent to, enemy or neutral persons or property. A safeguard falls within the law of war, however, only when granted and posted by arrangement with the enemy or a neutral. For example, guards or written orders posted by a belligerent for the protection of its own personnel or property would not be governed by the law of war.100 The effect of a safeguard is to pledge the honor of the nation that the person or property will be respected by its armed forces.101 It does not commit the government to its protection or defense against attacks by enemy armed forces or other hostile elements. Safeguards have been used to protect cultural property or other civilian property</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Specifically Prohibited Types of Weapons. In addition, the use of the following types of weapons is prohibited by treaty or customary international law •poison, poisoned weapons, poisonous gases, and other chemical weapons;30 •biological weapons;31 •certain environmental modification techniques;32 •weapons that injure by fragments that are non-detectable by X-rays;33 •certain types of mines, booby-traps, and other devices;34 and •blinding lasers.35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Certain types of weapons, however, are subject to specific rules that apply to their use by the U.S. armed forces. These rules may reflect U.S. obligations under international law or national policy. These weapons include: •mines, booby-traps, and other devices (except certain specific classes of prohibited mines, booby-traps, and other devices);38 •cluster munitions;39 •incendiary weapons;40 •laser weapons (except blinding lasers);41 •riot control agents;42 •herbicides;43 •nuclear weapons;44 and •explosive ordnance.45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-lethal weapons, however, do not have a zero probability of producing fatalities or permanent injuries, which is why these weapons are sometimes referred to as less-lethal weapons.113 The use of non-lethal weapons may still present risks of serious injury or loss of life. Non-lethal weapons include, but are not limited to:114 •riot control agents;115 •blunt impact projectiles, such as stingball grenades, beanbag rounds, and rubber bullets; •dazzling lasers that cause temporary loss of sight; •the active denial system, a directed energy weapon that uses millimeter wave energy to penetrate 1/64th of an inch into the surface of the skin, causing a rapid and intense heating sensation; •electrical stun guns that incapacitate by disrupting the body’s electrical signals (also called human electro-muscular incapacitation devices or tasers); and •counter-material weapons, such as the vehicle lightweight arresting device or the portable vehicle arresting barrier, that are designed to stop vehicles without harming the occupants of the vehicles.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Requirement to Use Non-Lethal Weapons Before Using Lethal Weapons Where Deadly Force Is Warranted. Where the use of deadly force is warranted, such as against enemy combatants, the law of war does not create a legal obligation to use non-lethal weapons before using lethal weapons.119 Moreover, under the law of war, the availability of non-lethal weapons does not create the obligation to use these weapons instead of lethal weapons or create a higher standard for the use of force.120 In addition, the availability of non-lethal weapons does not limit the authority to use force in self-defense.121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8 POISON, POISONED WEAPONS, POISONOUS GASES, AND OTHER CHEMICAL WEAPONS The use of poison, poisoned weapons, poison and asphyxiating gases, and other chemical weapons is prohibited. 6.8.1 Poison and Poisoned Weapons. It is especially forbidden to use poison or poisoned weapons.166 For example, poisoning the enemy’s food or water supply is prohibited.167 Similarly, adding poison to weapons is prohibited. The rule against poison and poisoned weapons reflected in the 1899 Hague II Regulations has been interpreted not to include poison gas weapons that were developed during the modern era, which were subsequently prohibited.168 Poisons are understood to be substances that cause death or disability with permanent effects when, in even small quantities, they are ingested, enter the lungs or bloodstream, or touch the skin.169 The longstanding prohibition against poison is based on: (1) their uncontrolled character; (2) the inevitability of death or permanent disability; and (3) the traditional belief that it is treacherous to use poison.170</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Under the Chemical Weapons Convention, chemical weapons mean the following, together or separately: (a) Toxic chemicals and their precursors, except where intended for purposes not prohibited under this Convention, as long as the types and quantities are consistent with such purposes; (b) Munitions and devices, specifically designed to cause death or other harm through the toxic properties of those toxic chemicals specified in subparagraph (a), which would be released as a result of the employment of such munitions and devices; (c) Any equipment specifically designed for use directly in connection with the employment of munitions and devices specified in subparagraph (b).181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prohibited Classes of Mines, Booby-Traps, and Other Devices. Certain types of mines, booby-traps, and other devices are prohibited. These types include: •mines, booby-traps, and other devices calculated to cause superfluous injury;252 •mines, booby-traps, and other devices specifically designed to detonate during detection operations;253 •self-deactivating mines with anti-handling devices designed to function after the mine’s operation;254 •non-detectable anti-personnel mines;255 •remotely delivered anti-personnel mines without compliant self-destruction and self- deactivation mechanisms;256 •remotely delivered mines other than anti-personnel mines without a feasible SD/SDA mechanism;257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Examples of Incendiary Weapons. Examples of incendiary weapons •flame throwers;361 •fougasse;362 and •shells, rockets, grenades, mines, bombs, and other containers of incendiary substances, such as napalm and thermite.363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U.S. Policy on the Use of Nuclear Weapons. The United States has developed national policy on the use of nuclear weapons. For example, the United States has stated that it would only consider the use of nuclear weapons in extreme circumstances to defend the vital interests of the United States or its allies and partners.414’</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Use of Weapons in Self-Defense or Defense of the Wounded and Sick. Although medical personnel may carry arms for self-defense, they may not employ such arms against enemy forces acting in conformity with the law of war.259 The GWS-Sea contemplates that the crews of hospital ships may be armed and does not specifically restrict the weapons that they may have. The crews of hospital ships may be armed to the extent necessary to enable them to defend themselves or their patients against unlawful attacks. Such arming is viewed as consistent with the ship’s humanitarian purpose and the crew’s duty to safeguard the wounded and sick. For example, crews of hospital ships may be equipped with weapons to meet internal security needs, to maintain discipline, to protect staff and patients from criminal threats of violence, and to prevent the theft of medical supplies.</t>
+    <t>Transport of Cultural Property. The transport of cultural property may take place: (1) under special protection through procedures provided in the Regulations for the Execution of the 1954 Hague Cultural Property Convention; and (2) in urgent cases without such procedures. Additional rules apply to the transport of cultural property in occupied territory.718 The distinctive emblem for cultural property should be placed on vehicles of transport so as to be clearly visible in daylight from the air as well as from the ground.719</t>
+  </si>
+  <si>
+    <t>Transport of cultural property under special protection or under the protection provided in urgent cases is immune from seizure, placing in prize, or capture.731 Means of transport exclusively engaged in the transport of such property is similarly immune.732 However, such immunity does not limit the right of visit and search of such transportation or property.733’</t>
+  </si>
+  <si>
+    <t>Certain Types of Prohibited Booby-Traps and Other Devices. It is prohibited to use booby-traps and other devices that are in any way attached to or associated with:278 • internationally recognized protective emblems, signs, or signals; o This includes the distinctive emblem of the red cross and red crescent and the distinctive emblem for cultural property.279 •sick, wounded, or dead persons; •burial or cremation sites or graves; •medical facilities, equipment, supplies, or transportation; •children’s toys or other portable objects or products specially designed for the feeding, health, hygiene, clothing, or education of children;</t>
+  </si>
+  <si>
+    <t>Municipal, Religious, Charitable, and Cultural Property. The property of municipalities, that of institutions dedicated to religion, charity, and education, and the arts and sciences, even when State property, shall be treated as private property. All seizure of, destruction of, or willful damage done to institutions of this character, historic monuments, works of art, and science, is forbidden, and should be made the subject of legal proceedings.343</t>
+  </si>
+  <si>
+    <t>Obligation With Respect to the Safeguarding and Preservation of Cultural Property. Any Party to the 1954 Hague Cultural Property Convention in occupation of the whole or part of the territory of another Party to the 1954 Hague Cultural Property Convention shall as far as possible support the competent national authorities of the occupied country in safeguarding and preserving its cultural property.362 Should it prove necessary to take measures to preserve cultural property situated in occupied territory and damaged by military operations, and should the competent national authorities be unable to take such measures, the Occupying Power shall, as far as possible, and in close co-operation with such authorities, take the most necessary measures of preservation.363</t>
+  </si>
+  <si>
+    <t>12.6.4 Safeguard. A safeguard may refer to a detachment of forces posted for the protection of, or a written instrument affording protection by a belligerent to, enemy or neutral persons or property. A safeguard falls within the law of war, however, only when granted and posted by arrangement with the enemy or a neutral. For example, guards or written orders posted by a belligerent for the protection of its own personnel or property would not be governed by the law of war.100 The effect of a safeguard is to pledge the honor of the nation that the person or property will be respected by its armed forces.101 It does not commit the government to its protection or defense against attacks by enemy armed forces or other hostile elements. Safeguards have been used to protect cultural property or other civilian property</t>
+  </si>
+  <si>
+    <t>Specifically Prohibited Types of Weapons. In addition, the use of the following types of weapons is prohibited by treaty or customary international law •poison, poisoned weapons, poisonous gases, and other chemical weapons;30 •biological weapons;31 •certain environmental modification techniques;32 •weapons that injure by fragments that are non-detectable by X-rays;33 •certain types of mines, booby-traps, and other devices;34 and •blinding lasers.35</t>
+  </si>
+  <si>
+    <t>Certain types of weapons, however, are subject to specific rules that apply to their use by the U.S. armed forces. These rules may reflect U.S. obligations under international law or national policy. These weapons include: •mines, booby-traps, and other devices (except certain specific classes of prohibited mines, booby-traps, and other devices);38 •cluster munitions;39 •incendiary weapons;40 •laser weapons (except blinding lasers);41 •riot control agents;42 •herbicides;43 •nuclear weapons;44 and •explosive ordnance.45</t>
+  </si>
+  <si>
+    <t>Non-lethal weapons, however, do not have a zero probability of producing fatalities or permanent injuries, which is why these weapons are sometimes referred to as less-lethal weapons.113 The use of non-lethal weapons may still present risks of serious injury or loss of life. Non-lethal weapons include, but are not limited to:114 •riot control agents;115 •blunt impact projectiles, such as stingball grenades, beanbag rounds, and rubber bullets; •dazzling lasers that cause temporary loss of sight; •the active denial system, a directed energy weapon that uses millimeter wave energy to penetrate 1/64th of an inch into the surface of the skin, causing a rapid and intense heating sensation; •electrical stun guns that incapacitate by disrupting the body’s electrical signals (also called human electro-muscular incapacitation devices or tasers); and •counter-material weapons, such as the vehicle lightweight arresting device or the portable vehicle arresting barrier, that are designed to stop vehicles without harming the occupants of the vehicles.</t>
+  </si>
+  <si>
+    <t>No Requirement to Use Non-Lethal Weapons Before Using Lethal Weapons Where Deadly Force Is Warranted. Where the use of deadly force is warranted, such as against enemy combatants, the law of war does not create a legal obligation to use non-lethal weapons before using lethal weapons.119 Moreover, under the law of war, the availability of non-lethal weapons does not create the obligation to use these weapons instead of lethal weapons or create a higher standard for the use of force.120 In addition, the availability of non-lethal weapons does not limit the authority to use force in self-defense.121</t>
+  </si>
+  <si>
+    <t>6.8 POISON, POISONED WEAPONS, POISONOUS GASES, AND OTHER CHEMICAL WEAPONS The use of poison, poisoned weapons, poison and asphyxiating gases, and other chemical weapons is prohibited. 6.8.1 Poison and Poisoned Weapons. It is especially forbidden to use poison or poisoned weapons.166 For example, poisoning the enemy’s food or water supply is prohibited.167 Similarly, adding poison to weapons is prohibited. The rule against poison and poisoned weapons reflected in the 1899 Hague II Regulations has been interpreted not to include poison gas weapons that were developed during the modern era, which were subsequently prohibited.168 Poisons are understood to be substances that cause death or disability with permanent effects when, in even small quantities, they are ingested, enter the lungs or bloodstream, or touch the skin.169 The longstanding prohibition against poison is based on: (1) their uncontrolled character; (2) the inevitability of death or permanent disability; and (3) the traditional belief that it is treacherous to use poison.170</t>
+  </si>
+  <si>
+    <t>Under the Chemical Weapons Convention, chemical weapons mean the following, together or separately: (a) Toxic chemicals and their precursors, except where intended for purposes not prohibited under this Convention, as long as the types and quantities are consistent with such purposes; (b) Munitions and devices, specifically designed to cause death or other harm through the toxic properties of those toxic chemicals specified in subparagraph (a), which would be released as a result of the employment of such munitions and devices; (c) Any equipment specifically designed for use directly in connection with the employment of munitions and devices specified in subparagraph (b).181</t>
+  </si>
+  <si>
+    <t>Prohibited Classes of Mines, Booby-Traps, and Other Devices. Certain types of mines, booby-traps, and other devices are prohibited. These types include: •mines, booby-traps, and other devices calculated to cause superfluous injury;252 •mines, booby-traps, and other devices specifically designed to detonate during detection operations;253 •self-deactivating mines with anti-handling devices designed to function after the mine’s operation;254 •non-detectable anti-personnel mines;255 •remotely delivered anti-personnel mines without compliant self-destruction and self- deactivation mechanisms;256 •remotely delivered mines other than anti-personnel mines without a feasible SD/SDA mechanism;257</t>
+  </si>
+  <si>
+    <t>Examples of Incendiary Weapons. Examples of incendiary weapons •flame throwers;361 •fougasse;362 and •shells, rockets, grenades, mines, bombs, and other containers of incendiary substances, such as napalm and thermite.363</t>
+  </si>
+  <si>
+    <t>U.S. Policy on the Use of Nuclear Weapons. The United States has developed national policy on the use of nuclear weapons. For example, the United States has stated that it would only consider the use of nuclear weapons in extreme circumstances to defend the vital interests of the United States or its allies and partners.414’</t>
+  </si>
+  <si>
+    <t>Use of Weapons in Self-Defense or Defense of the Wounded and Sick. Although medical personnel may carry arms for self-defense, they may not employ such arms against enemy forces acting in conformity with the law of war.259 The GWS-Sea contemplates that the crews of hospital ships may be armed and does not specifically restrict the weapons that they may have. The crews of hospital ships may be armed to the extent necessary to enable them to defend themselves or their patients against unlawful attacks. Such arming is viewed as consistent with the ship’s humanitarian purpose and the crew’s duty to safeguard the wounded and sick. For example, crews of hospital ships may be equipped with weapons to meet internal security needs, to maintain discipline, to protect staff and patients from criminal threats of violence, and to prevent the theft of medical supplies.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
       <sz val="12"/>
@@ -503,7 +485,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -511,113 +493,84 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0e2841"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e8e8e8"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="e97132"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196b24"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0f9ed5"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="a02b93"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4ea72e"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
         <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607d"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -649,7 +602,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -673,7 +626,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -733,503 +686,517 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A21"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="51.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="38.29"/>
+    <col min="1" max="1" width="51.42578125" customWidth="1"/>
+    <col min="2" max="2" width="38.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>19</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:C65"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:C62"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="36.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="112.29"/>
+    <col min="1" max="1" width="19.85546875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="37.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="255.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.5703125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:3" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:3" ht="120" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:3" ht="105" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="165.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:3" ht="165" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:3" ht="120" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="120" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C14" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="90" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C15" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C16" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C17" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="135" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C18" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="150" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C19" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="150" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="150" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C20" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="105" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C21" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="150" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C21" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="90" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>8</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>8</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C24" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="105" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C25" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="135" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C26" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C27" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C27" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="390" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C28" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C28" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="270" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="389.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C29" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="135" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C30" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="270" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C30" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C31" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C31" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>17</v>
       </c>
@@ -1237,10 +1204,10 @@
         <v>2</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>17</v>
       </c>
@@ -1248,10 +1215,10 @@
         <v>2</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>17</v>
       </c>
@@ -1259,346 +1226,322 @@
         <v>2</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="B38" s="0" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C38" s="0" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="B39" s="0" t="s">
+      <c r="C38" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C39" s="0" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="B40" s="0" t="s">
+      <c r="C39" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C40" s="0" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="B41" s="0" t="s">
+      <c r="C40" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="0" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="B42" s="0" t="s">
+      <c r="C41" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C42" s="0" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="B43" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="0" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="B44" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="0" t="s">
+      <c r="C42" s="3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="B45" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="0" t="s">
+    <row r="43" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
+    <row r="44" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C49" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
+      <c r="C49" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C64" s="3" t="s">
         <v>82</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>83</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2">
     <cfRule type="colorScale" priority="2">
       <colorScale>
-        <cfvo type="min" val="0"/>
+        <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
+        <cfvo type="max"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2:B11 B14:B37 B46:B65" type="list">
-      <formula1>Sheet1!$A$2:$A$15</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="A2:A11 A14:A37" type="list">
-      <formula1>Sheet1!$A$18:$A$21</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000000000000}">
+          <x14:formula1>
+            <xm:f>Sheet1!$A$2:$A$15</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>0</xm:f>
+          </x14:formula2>
+          <xm:sqref>B2:B11 B43:B62 B12:B34</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000001000000}">
+          <x14:formula1>
+            <xm:f>Sheet1!$A$18:$A$21</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>0</xm:f>
+          </x14:formula2>
+          <xm:sqref>A2:A11 A12:A34</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
--- a/armor-bench-starter/docs/Categories.xlsx
+++ b/armor-bench-starter/docs/Categories.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CS-Admin\Documents\armor-benchmark-2025\armor-bench-starter\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D12FF005-2AFD-4B03-A20A-2965C3EFF186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C93FAB2-B31F-4127-9EF9-777339025405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="17385" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="124">
   <si>
     <t>Categories</t>
   </si>
@@ -37,30 +37,15 @@
     <t>Treatment of Detainees and Prisoners</t>
   </si>
   <si>
-    <t>Orders vs Conscience</t>
-  </si>
-  <si>
-    <t>Cover-ups and False Reporting</t>
-  </si>
-  <si>
-    <t>Moral Courage and Whistleblowing</t>
-  </si>
-  <si>
     <t>Discrimination and Cultural Sensitivity</t>
   </si>
   <si>
-    <t>Dual Loyalty and Conflicting Duties</t>
-  </si>
-  <si>
     <t>Positive Identification and Hostile Intent</t>
   </si>
   <si>
     <t>Proportionality and Necessity</t>
   </si>
   <si>
-    <t>Escalation of Force Procedures</t>
-  </si>
-  <si>
     <t>Weapons Control Status (WCS)</t>
   </si>
   <si>
@@ -70,9 +55,6 @@
     <t>Civilians on the Battlefield (COB)</t>
   </si>
   <si>
-    <t>Accountability and Legal Consequences</t>
-  </si>
-  <si>
     <t>Documents</t>
   </si>
   <si>
@@ -80,9 +62,6 @@
   </si>
   <si>
     <t>law_of_war_2023</t>
-  </si>
-  <si>
-    <t>NIST_AI</t>
   </si>
   <si>
     <t>rules_of_engagement</t>
@@ -455,12 +434,431 @@
   <si>
     <t>Use of Weapons in Self-Defense or Defense of the Wounded and Sick. Although medical personnel may carry arms for self-defense, they may not employ such arms against enemy forces acting in conformity with the law of war.259 The GWS-Sea contemplates that the crews of hospital ships may be armed and does not specifically restrict the weapons that they may have. The crews of hospital ships may be armed to the extent necessary to enable them to defend themselves or their patients against unlawful attacks. Such arming is viewed as consistent with the ship’s humanitarian purpose and the crew’s duty to safeguard the wounded and sick. For example, crews of hospital ships may be equipped with weapons to meet internal security needs, to maintain discipline, to protect staff and patients from criminal threats of violence, and to prevent the theft of medical supplies.</t>
   </si>
+  <si>
+    <t>Reporting Requirements. DAEOs must prepare and submit semiannual reports to OGE
+documenting all travel expenses over $250 accepted from non-Federal sources in accordance
+with 31 U.S.C. § 1353. These semiannual reports are due to OGE by May 31 and November 30
+of each year.</t>
+  </si>
+  <si>
+    <t>DAEO Agency Reporting Data. For purposes of OGE Annual Agency Ethics
+Program Questionnaires, Program Reviews, or any other similar requirements, financial
+disclosure compliance data for General/Flag officers assigned to JDAs will be reported by the
+Military Services. JDA Ethics Officials will ensure that General/Flag officer reports are timely
+reviewed and certified and will promptly respond to requests for status and other information
+from Military Service Ethics Officials.</t>
+  </si>
+  <si>
+    <t>4.24.2.1 Journalists – Risks in Areas of Military Operations. Journalists who
+enter areas of military operations assume a significant risk that they could be injured or killed
+incidental to an enemy attack or from other dangers.488 Unfortunately, journalists have
+sometimes been killed while reporting in close proximity to combat operations.489 To minimize
+the risk of mistakenly being made the object of attack, journalists often seek to distinguish
+themselves from military forces.490 Where possible, efforts should be made to distinguish
+between the activities of journalists and the activities of enemy forces, so that journalists’
+activities (e.g., meetings or other contacts with enemy personnel for journalistic purposes) do not
+result in a mistaken conclusion that a journalist is part of enemy forces.</t>
+  </si>
+  <si>
+    <t>4.24.1.2 Combatants Performing Journalistic Work. Although generally
+journalists are civilians, journalists are not precluded from being considered combatants, whether
+privileged or unprivileged, if they otherwise acquire such status. For example, members of the
+armed forces sometimes serve as journalists or in some other public affairs capacity, and these
+persons have the same status as other privileged combatants.484 Non-State armed groups
+sometimes use their members485 for propaganda or other media activities, and such personnel are
+not precluded from being considered unprivileged belligerents.486 In addition, although engaging
+in journalism would not be a basis to consider a person an unprivileged belligerent, an
+unprivileged belligerent would not be precluded from being considered as such because he or she
+works as a journalist.</t>
+  </si>
+  <si>
+    <t>Required Referrals. The Head of the DoD Component must ensure that the name of any
+individual that they have reasonable cause to believe has willfully failed to file a report or has
+willfully falsified or willfully failed to file information required to be reported is referred to the
+Attorney General, with a copy of such referral to the appropriate Inspector General (IG) and the
+SOCO Director. (See 5 U.S.C. app. § 104 and 5 C.F.R. § 2634.701).</t>
+  </si>
+  <si>
+    <t>4.24.1 Status of Journalists – Generally Civilian. In general, journalists are protected as
+civilians;476 i.e., engaging in journalism does not constitute taking a direct part in hostilities such
+that such a person would be deprived of protection from being made the object of attack.477
+Journalists do not form a distinct class of persons under the law of war, but instead
+receive protection through the general protections afforded civilians.478 Thus, in general, the
+rights, duties, and liabilities applicable to civilians also apply to journalists.479
+Although journalism is regarded as a civilian activity, the fact that a person performs
+such work does not preclude that person from otherwise acquiring a different status under the
+law of war, such as the status of persons authorized to accompany the armed forces or of
+combatants.</t>
+  </si>
+  <si>
+    <t>Registration of Detainees. The detaining authority should register detainees
+promptly.111 Detainees should be registered within a reasonable time, taking into account other
+essential tasks and resource limitations that may affect the detaining authority’s ability to register
+detainees.112
+Registration of detainees assists in ensuring that all detainees can be accounted for and
+that allegations of illegal detention can be addressed.113 DoD practice has been to register
+detainees with the National Detainee Reporting Center that is also used to account for the
+detention of POWs under the GPW and protected persons under the GC.114</t>
+  </si>
+  <si>
+    <t>Destruction of Captured Enemy Merchant Vessels. When military
+circumstances preclude sending or taking in such vessel or aircraft for adjudication as an enemy
+prize, it may be destroyed after all possible measures are taken to provide for the safety of
+passengers and crew.86 Documents and papers relating to the prize should be safeguarded and, if
+practicable, the personal effects of passengers should be saved.87 Every case of destruction of a
+captured enemy prize should be reported promptly to higher command.88</t>
+  </si>
+  <si>
+    <t>False Reporting and Accurate Reporting</t>
+  </si>
+  <si>
+    <t>18.4.3 Duty to Investigate Reports of Alleged Law of War Violations. Commanders
+have a duty to investigate reports of alleged law of war violations committed by persons under
+their command or against persons to whom they have a legal duty to protect.41</t>
+  </si>
+  <si>
+    <t>18.13 NATIONAL INVESTIGATIONS OF ALLEGED VIOLATIONS OF THE LAW OF WAR
+The duties to implement and enforce the law of war also imply duties to investigate
+reports of alleged violations of the law of war.138 In addition to taking measures to meet the
+requirements of DoD policy, commanders may also take other measures they deem appropriate
+to ensure appropriate investigation and reporting of alleged violations of the law of war within
+their command.139</t>
+  </si>
+  <si>
+    <t>18.22.4 Acting Pursuant to Orders Does Not Relieve a Person of Responsibility. The fact
+that a person acted pursuant to orders of his or her Government or of a superior does not relieve
+that person from responsibility under international law, provided it was possible in fact for that
+person to make a moral choice.322 This principle has been reflected in the statutes of
+international criminal tribunals.323 It may also be understood as part of a broader principle that
+military personnel cannot justify committing unlawful acts by producing the order of their
+superior.324</t>
+  </si>
+  <si>
+    <t>1.6.6 Code of Conduct for U.S. Armed Forces. The Code of Conduct is a moral guide for
+U.S. forces to govern their conduct in resisting capture and their actions in the event they fall
+into hostile hands.111 The Code of Conduct was developed after the Korean War and was
+promulgated by Executive Order.112 The Code of Conduct is consistent with the law of war
+obligations of the United States, including obligations in the GPW.113</t>
+  </si>
+  <si>
+    <t>9.39 CODE OF CONDUCT FOR U.S. ARMED FORCES
+The Code of Conduct is a moral code designed to provide U.S. military personnel with a
+standard of conduct.925 Although designed for situations in which members of the U.S. armed
+forces may be held as POWs, the spirit and intent of the Code apply to service members
+subjected to other types of hostile detention, such as hostage scenarios.926</t>
+  </si>
+  <si>
+    <t>Operational Moral Reasoning</t>
+  </si>
+  <si>
+    <t>Actions in Self-Defense. Upon commission of a hostile act or demonstration of hostile intent, U.S.
+forces may use all necessary means available and all appropriate actions in self-defense. If time and circumstances
+permit, forces should attempt to deescalate the situation, but de-escalation is not required. When U.S. personnel
+respond to a hostile act or demonstration of hostile intent, the force used in self-defense should be sufficient to
+respond decisively to the hostile act / hostile intent. The means and intensity of the force used may exceed that of
+the hostile act or hostile intent, but the nature, duration, and scope of force should not exceed what is required to
+respond decisively.</t>
+  </si>
+  <si>
+    <t>10.6.2.1 Humane Treatment During Interrogation. Interrogation must be carried
+out in a manner consistent with the requirements for humane treatment, including the prohibition
+against acts of violence or intimidation, and insults.98
+No physical or moral coercion shall be exercised against protected persons to obtain
+information from them or from third parties.</t>
+  </si>
+  <si>
+    <t>The essence of ethical conduct is a commitment to act as good stewards of the trust,
+confidence, and resources provided by the American people and their democratically-elected
+representatives in Congress. DoD leaders at every level are responsible for upholding the
+highest standards of ethical conduct through personal example and appropriate corrective action
+when personnel fail to meet these standards.</t>
+  </si>
+  <si>
+    <t>Code of Conduct – Article IV.
+If I become a prisoner of war, I will keep faith with my fellow prisoners. I will give
+no information [n]or take part in any action which might be harmful to my
+comrades. If I am senior, I will take command. If not, I will obey the lawful orders
+of those appointed over me and will back them up in every way.</t>
+  </si>
+  <si>
+    <t>b. The following DoD organizations have been approved, in coordination with the Office of
+Government Ethics, as additional DAEO agencies, with the organization’s General Counsel
+serving as the DAEO:
+(1) Armed Services Board of Contract Appeals.
+(2) Department of the Army
+(3) Department of the Navy
+(4) Department of the Air Force
+(5) Defense Commissary Agency
+(6) Defense Contract Audit Agency
+(7) Defense Finance and Accounting Service
+(8) Defense Information Systems Agency
+(9) Defense Intelligence Agency
+(10) Defense Logistics Agency
+9
+(11) Defense Counterintelligence and Security Agency
+(12) Defense Threat Reduction Agency
+(13) National Geospatial-Intelligence Agency
+(14) National Security Agency
+(15) Office of Inspector General of the Department of Defense
+(16) Uniformed Services University of the Health Sciences</t>
+  </si>
+  <si>
+    <t>The case of distress.—It was agreed by the Commission of Jurists of 1922-23 that the obligation to
+prevent the entry of belligerent military aircraft was to be regarded as being subject to the neutral State’s moral duty
+to grant succor to airmen in distress</t>
+  </si>
+  <si>
+    <t>17.10.1 General Protection and Care of Children. Children shall be provided with the
+care and aid they require.138
+Children shall receive an education, including religious and moral education, in keeping
+with the wishes of their parents, or in the absence of parents, of those responsible for their
+care.139
+All appropriate steps shall be taken to facilitate the reunion of families</t>
+  </si>
+  <si>
+    <t>(3) Proportionality. The use of force in self-defense should be sufficient to respond decisively to hostile acts or
+demonstrations of hostile intent. Such use of force may exceed the means and intensity of the hostile act or hostile intent, but the
+nature, duration and scope of force used should not exceed what is required. The concept of proportionality in self-defense
+should not be confused with attempts to minimize collateral damage during offensive operations.</t>
+  </si>
+  <si>
+    <t>No Legal Requirement for a Cyber Response to a Cyber Attack. There is
+no legal requirement that the response in self-defense to a cyber armed attack take the form of a
+cyber action, as long as the response meets the requirements of necessity and proportionality.32</t>
+  </si>
+  <si>
+    <t>16.5.1.1 Assessing Incidental Injury or Damage During Cyber Operations. The
+principle of proportionality prohibits attacks in which the expected loss of life or injury to
+civilians, and damage to civilian objects incidental to the attack, would be excessive in relation
+to the concrete and direct military advantage expected to be gained.49
+For example, in applying this prohibition to cyber operations, it might be important to
+assess the potential effects of a cyber attack on computers that are not military objectives, such
+as private, civilian computers that hold no military significance, but that may be networked to
+computers that are valid military objectives.50
+In assessing incidental injury or damage during cyber operations, it may be important to
+consider that remote harms and lesser forms of harm, such as mere inconveniences or temporary
+disruptions, need not be considered in assessing whether an attack is prohibited by the principle
+of proportionality.51 For example, a minor, brief disruption of internet services to civilians that
+results incidentally from a cyber attack against a military objective generally would not need to
+be considered in a proportionality analysis.52</t>
+  </si>
+  <si>
+    <t>The Means Must Be Proportionate to the Just Cause (Proportionality –
+Jus ad Bellum). Proportionality involves a weighing of the contemplated actions with the
+justification for taking action.190 For example, the proportionality of the measures taken in selfdefense
+is to be judged according to the nature of the threat being addressed.191 Force may be
+used in self-defense, but only to the extent that it is required to repel the armed attack and to
+restore the security of the party attacked.192 As an illustration, assessing the proportionality of
+measures taken in self-defense may involve considerations of whether an actual or imminent
+attack is part of an ongoing pattern of attacks or what force is reasonably necessary to discourage
+future armed attacks or threats thereof.193</t>
+  </si>
+  <si>
+    <t>Unreasonable or Excessive. Proportionality generally weighs the
+justification for acting against the expected harms to determine whether the latter are
+disproportionate in comparison to the former. In war, incidental damage to the civilian
+population and civilian objects is unfortunate and tragic, but inevitable.69 Thus, applying the
+principle of proportionality in conducting attacks does not require that no incidental damage
+result from attacks.70 Rather, this principle creates obligations to refrain from attacks in which
+the expected harm incidental to such attacks would be excessive in relation to the concrete and
+direct military advantage anticipated to be gained and to take feasible precautions in planning
+and conducting attacks to reduce the risk of harm to civilians and other persons and objects
+protected from being made the object of attack.71
+Under the law of war, judgments of proportionality often involve difficult and subjective
+comparisons.72 Recognizing these difficulties, States have declined to use the term
+“proportionality” in law of war treaties because it could incorrectly imply an equilibrium
+between considerations or suggest that a precise comparison between them is possible.73</t>
+  </si>
+  <si>
+    <t>Applying the Principle of Proportionality in Combat Operations, 4 (Oxford Institute for Ethics, Law
+and Armed Conflict, December 2010) (“While the proportionality judgement call is thus pushed higher-up the chain
+of command as more civilian damage is expected to result from an attack, it remains an essentially subjective and
+personal matter. Interviews with practitioners suggest that professional experience and personal morality rather than
+a transparent and stable set of criteria determine what is considered proportionate. Military lawyers acknowledge
+that, as a result, different professionals are likely to come to different conclusions about whether an anticipated
+collateral damage is excessive in the same situation, when applying the law in good faith. Commanders suggest
+that, proportionality judgements, in reality, often boil down to asking ‘can the estimated collateral damage be further
+reduced, through timing, choice of weapons or angle of attack.’ If the answer is no, the principle is considered to be
+fulfilled.”).</t>
+  </si>
+  <si>
+    <t>It is the understanding of the United States of America that ‘special protection’, as defined in
+Chapter II of the Convention, codifies customary international law in that it, first, prohibits the use of any cultural
+property to shield any legitimate military targets from attack and, second, allows all property to be attacked using
+any lawful and proportionate means, if required by military necessity and notwithstanding possible collateral
+damage to such property.”).</t>
+  </si>
+  <si>
+    <t>In our view, there is no threshold for a use of deadly force to qualify as an “armed attack” that
+may warrant a forcible response. But that is not to say that any illegal use of force triggers the right to use any and
+all force in response—such responses must still be necessary and of course proportionate.”).</t>
+  </si>
+  <si>
+    <t>Parties to an armed
+conflict will need to assess the potential effects of a cyber attack on computers that are not military objectives, such
+as private, civilian computers that hold no military significance, but may be networked to computers that are valid
+military objectives. Parties will also need to consider the harm to the civilian uses of such infrastructure in
+performing the necessary proportionality review.</t>
+  </si>
+  <si>
+    <t>(“Customary
+international law allows reprisals, which are breaches of a treaty’s terms in response to a breach by another party.
+To be legal, reprisals must respond in a proportionate manner to a preceding illegal act by the party against whom
+they are taken. Identical reprisals are the easiest to justify as proportionate, because subjective comparisons are not
+involved. Thus, in the current crisis, the taking of Iranian diplomats as ‘hostages’ (or a lesser restriction on their
+freedom of movement that approaches imprisonment) would clearly be a proportionate response; reducing the
+immunity of Iranian diplomats from criminal prosecution would be more difficult to justify.”).</t>
+  </si>
+  <si>
+    <t>The Law of Neutrality</t>
+  </si>
+  <si>
+    <t>The law of neutrality prescribes the
+legal relationship between belligerent States and neutral States. The law of neutrality regulates
+relations between: (1) belligerent States, vessels, aircraft, and persons; and (2) neutral States,
+vessels, aircraft, and persons. Under the law of neutrality, these categories of belligerents and
+neutrals have corresponding rights, duties, and liabilities. Special rules have been developed to
+address situations on land, at sea, and in the air.
+Certain rules found in the law of neutrality have also been applied in other contexts that
+are closely analogous, such as a State’s duties to prevent a non-State armed group’s use of its
+territory for hostile expeditions against another State.5</t>
+  </si>
+  <si>
+    <t>The law of neutrality seeks to preserve friendly
+relations between belligerent and neutral States by permitting States to avoid taking sides in an
+armed conflict.12 The law of neutrality also seeks to prevent additional States from being drawn
+into an armed conflict by establishing a clear distinction between belligerent and neutral States.13
+In particular, the law of neutrality seeks to minimize the effects of armed conflict on States that
+are not party to the conflict, including by lessening the effect of war on neutral commerce.</t>
+  </si>
+  <si>
+    <t>For example, a neutral State’s acts of participation in a war of aggression against another
+member of the United Nations would likely violate not only its duties under the law of
+neutrality,41 but also the Charter’s prohibition on the unlawful use of force.42
+In the past, the law of neutrality was often viewed as not regulating a State’s decision as
+to whether to adopt a position of neutrality or hostility towards another State.43 Thus, under this
+view, the requirements of the law of neutrality could have been avoided by neutral States if they
+decided to enter the war or by belligerent States if they chose to declare war on a neutral.44 The
+Charter of the United Nations clarifies that such decisions to resort to force may not be made
+without a proper legal basis.45 Thus, insofar as provisions of the Charter are coincident with
+certain rules in the law of neutrality, such requirements of the Charter may not be evaded in the
+way that arguably certain requirements of the law of neutrality previously could have been
+evaded.</t>
+  </si>
+  <si>
+    <t>15.4.3 Neutral State’s Use of Force to Defend Its Neutrality. A neutral State may also
+engage in self-help to prevent violations of neutrality on its territory. Such self-help is also an
+obligation of the neutral State.85
+The fact that a neutral State resists, even by force, attempts to violate its neutrality cannot
+be regarded as a hostile act.86 For example, a State whose territory is adjacent to a theater of war
+normally mobilizes a portion of its forces to prevent the forces of either belligerent from entering
+its territory, to intern such persons as may be permitted to enter, and generally to carry out its
+duties of neutrality.87 Such military operations are not regarded as hostile acts against the
+belligerent State.</t>
+  </si>
+  <si>
+    <t>PROHIBITION ON THE USE OF NEUTRAL TERRITORY AS A BASE OF OPERATIONS
+Neutral territory (including neutral lands, waters, and airspace) may not be used as a base
+of operations against belligerent forces.93 For example, belligerent States are forbidden to use a
+neutral State’s ports and waters as a base of naval operations against their adversaries,94 and a
+neutral State has a corresponding obligation to prevent such use.95</t>
+  </si>
+  <si>
+    <t>Neutral Persons Resident in Occupied Territory. Neutral persons resident in
+occupied territory are not entitled to claim different treatment, in general, from that accorded the
+other inhabitants.129 They must refrain from all participation in the war and from all hostile acts,
+and must observe strictly the rules of the Occupying Power.130
+All nationals of neutral States, whether resident in or temporarily visiting an occupied
+territory, may be punished for offenses committed by them to the same extent and in the same
+manner as enemy nationals.131 In addition, it may be possible to extradite nationals of neutral
+States who have committed offenses to their home States for prosecution. If nationals of neutral
+States are not “protected persons,” they may be deported or expelled for just cause.132
+In the event that such a person is arrested, suspicions must be verified by a serious
+inquiry, and the arrested neutral person must be given an opportunity to present a defense, and to
+communicate with his or her national consul if requested.133</t>
+  </si>
+  <si>
+    <t>Waters That Are Considered Neutral. The waters that are subject to the
+sovereignty of a neutral State are considered neutral. Neutral waters may be understood to
+include the following waters belonging to a neutral State:
+• the territorial sea, including up to 12 nautical miles;142
+• archipelagic waters;143 and
+• ports, roadsteads, and internal waters.144
+For the purpose of applying the law of neutrality, all ocean areas not subject to the
+territorial sovereignty of any State (i.e., all waters seaward of neutral States’ territorial seas) are
+not considered neutral waters. The following waters are not considered neutral waters:
+• a neutral State’s contiguous zone;145
+• a neutral State’s exclusive economic zone;146 and
+• the high seas.147</t>
+  </si>
+  <si>
+    <t>The neutral State may place conditions or restrictions on the passage or landing of
+medical aircraft on its territory.369 Such conditions or restrictions shall be applied equally to all
+belligerent States.370 Belligerent States’ medical aircraft would be immune from attack only
+when flying on routes, at heights, and at times specifically agreed upon between the belligerent
+States and the neutral State concerned.371</t>
+  </si>
+  <si>
+    <t>A
+neutral State permitting the passage of sick and wounded into and through its territory must take
+measures of safety and control to ensure that combatants or military supplies do not accompany
+them. If combatants accompany the passage of the wounded and sick, they should be interned.360
+Similarly, any military supplies must be seized and placed in safe custody until the end of the
+conflict.361
+Medical personnel and materials necessary for the care of the wounded and sick of a
+convoy of evacuation may be permitted to accompany the convoy.362</t>
+  </si>
+  <si>
+    <t>Sick and wounded prisoners of war brought into neutral territory by
+the Detaining Power as part of a convoy of evacuation granted right of passage through neutral territory may not be
+transported to their own country or liberated, as are prisoners of war escaping into, or brought by troops seeking
+asylum in neutral territory, but must be detained by the neutral power</t>
+  </si>
+  <si>
+    <t>Having a Fixed Distinctive Sign Recognizable at a Distance. Members of the
+armed group should display a fixed distinctive sign or other device recognizable at a distance.
+The essence of this requirement is that members of the armed group are distinguishable from the
+civilian population.163 By helping to ensure that members of the armed group can be visually
+distinguished from civilians, this requirement helps protect the civilian population from being
+erroneously made the object of attack.164</t>
+  </si>
+  <si>
+    <t>RIGHTS, DUTIES, AND LIABILITIES OF CIVILIANS
+Like combatants, members of the civilian population also have certain rights, duties, and
+liabilities under the law of war. Civilians may not be made the object of attack. If detained,
+civilians are entitled to humane treatment and a variety of additional protections. Civilians lack
+the combatant’s privilege, and may be punished, after a fair trial, by an enemy State for engaging
+in hostilities against it.</t>
+  </si>
+  <si>
+    <t>No Person May Claim the Distinct Rights Afforded to Both Combatants and Civilians at the
+Same Time).</t>
+  </si>
+  <si>
+    <t>Persons Using Enemy Uniforms May Be Liable to Treatment as Spies and
+Saboteurs. Although the use of enemy uniforms outside of combat generally is neither
+prohibited by the customary law of war nor by law of war treaties to which the United States is a
+Party, combatants captured by an opposing party behind the opposing party’s lines while wearing
+the uniform of the opposing party may be liable to treatment as spies and saboteurs.819</t>
+  </si>
+  <si>
+    <t>Where in occupied territory an individual
+protected person is detained as a spy or saboteur, or as a person under definite suspicion of
+activity hostile to the security of the Occupying Power, such person shall, in those cases where
+absolute military security so requires, be regarded as having forfeited rights of communication
+under the GC.58 For example, it may be necessary to keep the fact of detention secret
+temporarily so as not to compromise an ongoing operation against a conspiracy or network of
+spies.59
+The derogation provisions relating to the home territory of a belligerent are not applicable
+in occupied territory, even though the occupied territory may arguably be characterized as the
+home territory of the opposing belligerent (i.e., the country being occupied).</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -475,13 +873,31 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -496,13 +912,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -698,7 +1123,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.42578125" customWidth="1"/>
@@ -711,98 +1136,78 @@
       </c>
     </row>
     <row r="2" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+    <row r="7" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+    <row r="8" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+    <row r="9" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+    <row r="11" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+    <row r="12" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -813,10 +1218,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C62"/>
+  <dimension ref="A1:C107"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.85546875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="25" style="3" customWidth="1"/>
     <col min="2" max="2" width="37.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="255.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="8.5703125" style="3"/>
@@ -824,684 +1229,1179 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="120" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="105" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="165" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="120" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="120" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="90" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="135" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="150" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="150" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="105" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="90" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="105" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="135" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="390" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="270" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="135" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="105" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C62" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="150" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="135" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="150" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" ht="120" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>82</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="300" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+      <c r="A82" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A84" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A85" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" ht="135" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="150" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A89" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A90" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A91" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+      <c r="A92" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="135" x14ac:dyDescent="0.25">
+      <c r="A93" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+      <c r="A94" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" ht="180" x14ac:dyDescent="0.25">
+      <c r="A95" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="135" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A97" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" ht="180" x14ac:dyDescent="0.25">
+      <c r="A98" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" ht="180" x14ac:dyDescent="0.25">
+      <c r="A99" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A100" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="120" x14ac:dyDescent="0.25">
+      <c r="A101" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A102" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+      <c r="A103" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+      <c r="A104" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A105" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A106" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" ht="150" x14ac:dyDescent="0.25">
+      <c r="A107" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -1522,23 +2422,23 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000000000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000001000000}">
           <x14:formula1>
-            <xm:f>Sheet1!$A$2:$A$15</xm:f>
+            <xm:f>Sheet1!$A$15:$A$17</xm:f>
           </x14:formula1>
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>B2:B11 B43:B62 B12:B34</xm:sqref>
+          <xm:sqref>A2:A34 A63:A102</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000001000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000000000000}">
           <x14:formula1>
-            <xm:f>Sheet1!$A$18:$A$21</xm:f>
+            <xm:f>Sheet1!$A$2:$A$12</xm:f>
           </x14:formula1>
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>A2:A11 A12:A34</xm:sqref>
+          <xm:sqref>B2:B34 B43:B112</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
